--- a/data/raw/inventory/Week 32/Tonor/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 32/Tonor/Seller FBA Inventory (SP-API).xlsx
@@ -895,7 +895,7 @@
         <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -907,7 +907,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>5</v>
